--- a/kicad/ELSONIC/POWER_BD_SV6/POWER_BD_SV6_PL_SMD.xlsx
+++ b/kicad/ELSONIC/POWER_BD_SV6/POWER_BD_SV6_PL_SMD.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AllData\06_Embedded_Proj\KiCAD\ELSONIC\POWER_BD_SV6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF18C0D-5A63-4E3D-8A80-98794A692022}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20B06D8-5B89-46CD-967A-62DF861C9124}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="450" windowWidth="24960" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29640" yWindow="270" windowWidth="24960" windowHeight="15015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="POWER_BD_SV5" sheetId="1" r:id="rId1"/>
+    <sheet name="POWER_BD_SV6" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="144">
   <si>
     <t>Footprint</t>
   </si>
@@ -193,9 +193,6 @@
     <t>C11,C13</t>
   </si>
   <si>
-    <t>C76663</t>
-  </si>
-  <si>
     <t>LL4148</t>
   </si>
   <si>
@@ -265,199 +262,198 @@
     <t>R7,R8</t>
   </si>
   <si>
+    <t>TL431DBZ</t>
+  </si>
+  <si>
+    <t>VR1</t>
+  </si>
+  <si>
+    <t>01_MyFoot_ICs:SOT-23-3</t>
+  </si>
+  <si>
+    <t>C23892</t>
+  </si>
+  <si>
+    <t>LM7805_TO220</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>C21706</t>
+  </si>
+  <si>
+    <t>0.47R/1W/F</t>
+  </si>
+  <si>
+    <t>R3,R4</t>
+  </si>
+  <si>
+    <t>C21097</t>
+  </si>
+  <si>
+    <t>39K/F</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>C18008</t>
+  </si>
+  <si>
+    <t>820R/F</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>C17984</t>
+  </si>
+  <si>
+    <t>220R</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>C17957</t>
+  </si>
+  <si>
+    <t>4.7K</t>
+  </si>
+  <si>
+    <t>R6,R10</t>
+  </si>
+  <si>
+    <t>C17936</t>
+  </si>
+  <si>
+    <t>C17902</t>
+  </si>
+  <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>100R</t>
+  </si>
+  <si>
+    <t>R27</t>
+  </si>
+  <si>
+    <t>C17901</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>R30</t>
+  </si>
+  <si>
+    <t>C17900</t>
+  </si>
+  <si>
+    <t>1.2K/F</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>C17891</t>
+  </si>
+  <si>
+    <t>CC472/1kV</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C9192</t>
+  </si>
+  <si>
+    <t>CC471/1kV</t>
+  </si>
+  <si>
+    <t>C16,C17,C18</t>
+  </si>
+  <si>
+    <t>C9189</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>C4410</t>
+  </si>
+  <si>
+    <t>LED_SMD_KT_0805R</t>
+  </si>
+  <si>
+    <t>LED1,LED2</t>
+  </si>
+  <si>
+    <t>03_MyFoot_Active:LED_2012Metric</t>
+  </si>
+  <si>
+    <t>C2295</t>
+  </si>
+  <si>
+    <t>BZT52C22</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>03_MyFoot_Active:D_SOD-123</t>
+  </si>
+  <si>
+    <t>C2108</t>
+  </si>
+  <si>
+    <t>MLCC104</t>
+  </si>
+  <si>
+    <t>C9,C12,C26,C27,C28,C30</t>
+  </si>
+  <si>
+    <t>C1945</t>
+  </si>
+  <si>
+    <t>MLCC102</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>C1941</t>
+  </si>
+  <si>
+    <t>MLCC224</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C1857</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>C20617860</t>
+  </si>
+  <si>
+    <t>R11,R20</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>C25385</t>
-  </si>
-  <si>
-    <t>TL431DBZ</t>
-  </si>
-  <si>
-    <t>VR1</t>
-  </si>
-  <si>
-    <t>01_MyFoot_ICs:SOT-23-3</t>
-  </si>
-  <si>
-    <t>C23892</t>
-  </si>
-  <si>
-    <t>LM7805_TO220</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>C21706</t>
-  </si>
-  <si>
-    <t>0.47R/1W/F</t>
-  </si>
-  <si>
-    <t>R3,R4</t>
-  </si>
-  <si>
-    <t>C21097</t>
-  </si>
-  <si>
-    <t>39K/F</t>
-  </si>
-  <si>
-    <t>R19</t>
-  </si>
-  <si>
-    <t>C18008</t>
-  </si>
-  <si>
-    <t>820R/F</t>
-  </si>
-  <si>
-    <t>R12</t>
-  </si>
-  <si>
-    <t>C17984</t>
-  </si>
-  <si>
-    <t>220R</t>
-  </si>
-  <si>
-    <t>R23</t>
-  </si>
-  <si>
-    <t>C17957</t>
-  </si>
-  <si>
-    <t>4.7K</t>
-  </si>
-  <si>
-    <t>R6,R10</t>
-  </si>
-  <si>
-    <t>C17936</t>
-  </si>
-  <si>
-    <t>10K/F</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>C17902</t>
-  </si>
-  <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>R11</t>
-  </si>
-  <si>
-    <t>100R</t>
-  </si>
-  <si>
-    <t>R27</t>
-  </si>
-  <si>
-    <t>C17901</t>
-  </si>
-  <si>
-    <t>100K</t>
-  </si>
-  <si>
-    <t>R30</t>
-  </si>
-  <si>
-    <t>C17900</t>
-  </si>
-  <si>
-    <t>1.2K/F</t>
-  </si>
-  <si>
-    <t>R13</t>
-  </si>
-  <si>
-    <t>C17891</t>
-  </si>
-  <si>
-    <t>CC472/1kV</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>C9192</t>
-  </si>
-  <si>
-    <t>CC471/1kV</t>
-  </si>
-  <si>
-    <t>C16,C17,C18</t>
-  </si>
-  <si>
-    <t>C9189</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>C4410</t>
-  </si>
-  <si>
-    <t>LED_SMD_KT_0805R</t>
-  </si>
-  <si>
-    <t>LED1,LED2</t>
-  </si>
-  <si>
-    <t>03_MyFoot_Active:LED_2012Metric</t>
-  </si>
-  <si>
-    <t>C2295</t>
-  </si>
-  <si>
-    <t>BZT52C22</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>03_MyFoot_Active:D_SOD-123</t>
-  </si>
-  <si>
-    <t>C2108</t>
-  </si>
-  <si>
-    <t>MLCC104</t>
-  </si>
-  <si>
-    <t>C9,C12,C26,C27,C28,C30</t>
-  </si>
-  <si>
-    <t>C1945</t>
-  </si>
-  <si>
-    <t>MLCC102</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>C1941</t>
-  </si>
-  <si>
-    <t>MLCC224</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>C1857</t>
-  </si>
-  <si>
-    <t>Comment</t>
-  </si>
-  <si>
-    <t>Designator</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1447,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.25" customWidth="1"/>
@@ -1458,10 +1454,10 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -1677,225 +1673,225 @@
         <v>49</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>32</v>
@@ -1906,156 +1902,142 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>32</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
